--- a/dist/simple_exception_disease_2610.xlsx
+++ b/dist/simple_exception_disease_2610.xlsx
@@ -14916,7 +14916,7 @@
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>질병수술비 · 1-5종 수술비(plus 포함) · (질병)1-7종 수술비 · 상급종합병원질병수술비 · 종합병원질병수술비 · 질병수술비(특정2대·특정5대·특정6대질병제외)</t>
+          <t>질병수술비 · 1-5종 수술비(plus 포함) · (질병)1-7종 수술비 · 상급종합병원질병수술비 · 종합병원질병수술비 · 질병수술비(특정2대·특정5대·특정6대질병제외) · 130대질병수술비</t>
         </is>
       </c>
     </row>
